--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513669_FASEFINALBFFB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513669_FASEFINALBFFB4_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7317</v>
+        <v>3.2171</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2866</v>
+        <v>3.6886</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4714</v>
       </c>
       <c r="G2" t="n">
         <v>2.3194</v>
@@ -610,13 +610,13 @@
         <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0492</v>
+        <v>1.5346</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8542</v>
+        <v>1.2561</v>
       </c>
       <c r="U2" t="n">
-        <v>0.195</v>
+        <v>0.2785</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2211</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.082</v>
+        <v>2.839</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4736</v>
+        <v>2.0307</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6084</v>
+        <v>0.8083</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0019</v>
+        <v>0.5818</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2581</v>
+        <v>0.9853</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7438</v>
+        <v>-0.4035</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7663</v>
+        <v>0.437</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9963</v>
+        <v>1.0931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.77</v>
+        <v>-0.6561</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7644</v>
+        <v>0.1448</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7381</v>
+        <v>-0.1078</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0262</v>
+        <v>0.2527</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7789</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.921</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1421</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>1.969</v>
+        <v>1.4783</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7383999999999999</v>
+        <v>1.0669</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2307</v>
+        <v>0.4114</v>
       </c>
       <c r="V3" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.89</v>
+        <v>1.5005</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0272</v>
+        <v>2.7643</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8688</v>
+        <v>1.5733</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1584</v>
+        <v>1.191</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2727</v>
+        <v>1.0019</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3311</v>
+        <v>0.2581</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9416</v>
+        <v>0.7438</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0437</v>
+        <v>2.7663</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3547</v>
+        <v>1.9963</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6889</v>
+        <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>0.229</v>
+        <v>-1.7644</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0236</v>
+        <v>-1.7381</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2527</v>
+        <v>-0.0262</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9737</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9474</v>
+        <v>-2.921</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9737</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0076</v>
+        <v>1.6513</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7725</v>
+        <v>0.838</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2351</v>
+        <v>0.8133</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2795</v>
+        <v>0.89</v>
       </c>
       <c r="W4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7966</v>
+        <v>1.4353</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0718</v>
+        <v>0.3326</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7248</v>
+        <v>1.1027</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5818</v>
+        <v>2.2727</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9853</v>
+        <v>1.3311</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4035</v>
+        <v>0.9416</v>
       </c>
       <c r="J5" t="n">
-        <v>0.437</v>
+        <v>2.0437</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0931</v>
+        <v>1.3547</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6561</v>
+        <v>0.6889</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1448</v>
+        <v>0.229</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1078</v>
+        <v>-0.0236</v>
       </c>
       <c r="O5" t="n">
         <v>0.2527</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7789</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7526</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4359</v>
+        <v>0.4158</v>
       </c>
       <c r="T5" t="n">
-        <v>0.108</v>
+        <v>0.2363</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3279</v>
+        <v>0.1795</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.2795</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.5005</v>
-      </c>
       <c r="X5" t="n">
-        <v>-1.5005</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5695</v>
+        <v>1.4086</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6687</v>
+        <v>0.7968</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0993</v>
+        <v>0.6118</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4397</v>
+        <v>0.2665</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3124</v>
+        <v>-2.0387</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7522</v>
+        <v>2.3052</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0278</v>
+        <v>1.0691</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3388</v>
+        <v>-0.844</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6889</v>
+        <v>1.9131</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4119</v>
+        <v>-0.8025</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6513</v>
+        <v>-1.1947</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0632</v>
+        <v>0.3921</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3895</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3632</v>
+        <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0724</v>
+        <v>0.9211</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6147</v>
+        <v>0.4541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4578</v>
+        <v>0.467</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.3321</v>
+        <v>0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.3321</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.7539</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3363</v>
+        <v>1.9453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6118</v>
+        <v>-1.1914</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2665</v>
+        <v>0.1597</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0387</v>
+        <v>1.2747</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3052</v>
+        <v>-1.1151</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0691</v>
+        <v>1.2175</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.844</v>
+        <v>1.9142</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9131</v>
+        <v>-0.6967</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8025</v>
+        <v>-1.0578</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1947</v>
+        <v>-0.6394</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3921</v>
+        <v>-0.4184</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3895</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
         <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4605</v>
+        <v>0.2379</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0064</v>
+        <v>-0.1301</v>
       </c>
       <c r="U7" t="n">
-        <v>0.467</v>
+        <v>0.368</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6105</v>
+        <v>-0.2279</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2211</v>
+        <v>1.8316</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6105</v>
+        <v>-2.0595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6085</v>
+        <v>0.6724</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8834</v>
+        <v>1.7717</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2749</v>
+        <v>-1.0993</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1597</v>
+        <v>1.4397</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2747</v>
+        <v>-0.3124</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1151</v>
+        <v>1.7522</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2175</v>
+        <v>1.0278</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9142</v>
+        <v>0.3388</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6967</v>
+        <v>0.6889</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0578</v>
+        <v>0.4119</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6394</v>
+        <v>-0.6513</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4184</v>
+        <v>1.0632</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5579</v>
+        <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0926</v>
+        <v>2.1753</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.192</v>
+        <v>1.7176</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2845</v>
+        <v>0.4578</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2279</v>
+        <v>-3.3321</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8316</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.0595</v>
+        <v>-3.3321</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3882</v>
+        <v>-1.0335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0839</v>
+        <v>0.383</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4721</v>
+        <v>-1.4165</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2042</v>
@@ -1156,13 +1156,13 @@
         <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1576</v>
+        <v>0.197</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0711</v>
+        <v>0.3701</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2287</v>
+        <v>-0.1731</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2211</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5716</v>
+        <v>-1.0616</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5466</v>
+        <v>-2.1479</v>
       </c>
       <c r="F10" t="n">
-        <v>0.975</v>
+        <v>1.0863</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4029</v>
@@ -1234,13 +1234,13 @@
         <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1097</v>
+        <v>1.6197</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8869</v>
+        <v>1.2856</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2228</v>
+        <v>0.3341</v>
       </c>
       <c r="V10" t="n">
         <v>0.2795</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3359</v>
+        <v>-2.7612</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.062</v>
+        <v>-5.3831</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2738</v>
+        <v>2.6219</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0232</v>
+        <v>-1.8562</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4039</v>
+        <v>-1.0945</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6193</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1048</v>
+        <v>-1.7957</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1026</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2074</v>
+        <v>-1.2801</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9184</v>
+        <v>-0.0604</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5065</v>
+        <v>-0.5789</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4118</v>
+        <v>0.5185</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1684</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9474</v>
+        <v>-4.8684</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7789</v>
+        <v>2.1421</v>
       </c>
       <c r="S11" t="n">
-        <v>2.0183</v>
+        <v>0.5487</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4896</v>
+        <v>0.06</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.4887</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1626</v>
+        <v>1.2726</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5005</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6632</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3654</v>
+        <v>-3.8621</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.043</v>
+        <v>-0.5604</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6776</v>
+        <v>-3.3017</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8562</v>
+        <v>-2.0232</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0945</v>
+        <v>-0.4039</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-1.6193</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7957</v>
+        <v>-1.1048</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.1026</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2801</v>
+        <v>-1.2074</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0604</v>
+        <v>-0.9184</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5789</v>
+        <v>-0.5065</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5185</v>
+        <v>-0.4118</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.7263</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.8684</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1421</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0556</v>
+        <v>1.4921</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5999</v>
+        <v>0.9912</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5443</v>
+        <v>0.5009</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2726</v>
+        <v>-2.1626</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2211</v>
+        <v>1.5005</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0516</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1294</v>
+        <v>-5.0899</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7682</v>
+        <v>-3.8679</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3612</v>
+        <v>-1.2221</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1214</v>
@@ -1468,13 +1468,13 @@
         <v>0.1947</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4389</v>
+        <v>0.4783</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7448</v>
+        <v>0.6451</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.306</v>
+        <v>-0.1668</v>
       </c>
       <c r="V13" t="n">
         <v>0.2795</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.026900000000002</v>
+        <v>-0.7176999999999989</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2533000000000003</v>
+        <v>0.5627</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2802</v>
+        <v>-1.2804</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5662000000000007</v>
+        <v>-0.5661999999999998</v>
       </c>
       <c r="H14" t="n">
         <v>-3.322500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2.756400000000001</v>
+        <v>2.7564</v>
       </c>
       <c r="J14" t="n">
         <v>6.137099999999998</v>
@@ -1546,13 +1546,13 @@
         <v>15.5789</v>
       </c>
       <c r="S14" t="n">
-        <v>12.4409</v>
+        <v>12.7501</v>
       </c>
       <c r="T14" t="n">
-        <v>8.4819</v>
+        <v>8.790899999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.959099999999999</v>
+        <v>3.9593</v>
       </c>
       <c r="V14" t="n">
         <v>-5.112200000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6639</v>
+        <v>5.5485</v>
       </c>
       <c r="E15" t="n">
-        <v>2.11</v>
+        <v>2.6084</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5539</v>
+        <v>2.9401</v>
       </c>
       <c r="G15" t="n">
         <v>1.5463</v>
@@ -1624,13 +1624,13 @@
         <v>3.7</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.604</v>
+        <v>-0.7194</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2985</v>
+        <v>-0.8002</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3055</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>3.9426</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.201</v>
+        <v>5.0818</v>
       </c>
       <c r="E16" t="n">
         <v>5.4414</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2404</v>
+        <v>-0.3595</v>
       </c>
       <c r="G16" t="n">
         <v>3.5659</v>
@@ -1702,13 +1702,13 @@
         <v>3.7</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3707</v>
+        <v>-1.4898</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4485</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.9222</v>
+        <v>-1.0413</v>
       </c>
       <c r="V16" t="n">
         <v>0.2795</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6175</v>
+        <v>4.0254</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1236</v>
+        <v>0.4745</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7411</v>
+        <v>3.5509</v>
       </c>
       <c r="G17" t="n">
         <v>3.8696</v>
@@ -1780,13 +1780,13 @@
         <v>3.5053</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.7263</v>
+        <v>-1.3184</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.113</v>
+        <v>-0.515</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.6133</v>
+        <v>-0.8034</v>
       </c>
       <c r="V17" t="n">
         <v>0.89</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3523</v>
+        <v>0.6343</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7651</v>
+        <v>1.8648</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4128</v>
+        <v>-1.2305</v>
       </c>
       <c r="G18" t="n">
         <v>1.2659</v>
@@ -1858,13 +1858,13 @@
         <v>2.7263</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8346</v>
+        <v>-0.5526</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5104</v>
+        <v>-0.4107</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3242</v>
+        <v>-0.1419</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8316</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1072</v>
+        <v>-0.0559</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0188</v>
+        <v>-1.8388</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.126</v>
+        <v>1.7829</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.212</v>
+        <v>-3.599</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1565</v>
+        <v>-3.2456</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0555</v>
+        <v>-0.3534</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1971</v>
+        <v>-2.711</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1565</v>
+        <v>-2.1115</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-0.5995</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4091</v>
+        <v>-0.888</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3131</v>
+        <v>-1.1342</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.096</v>
+        <v>0.2461</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5842000000000001</v>
+        <v>3.3105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7526</v>
+        <v>3.3105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2412</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7107</v>
+        <v>-0.3488</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4695</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.371</v>
+        <v>-0.302</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2784</v>
+        <v>-0.7786</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6494</v>
+        <v>0.4766</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1177</v>
+        <v>-1.212</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5683</v>
+        <v>-0.1565</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4506</v>
+        <v>-1.0555</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9099</v>
+        <v>0.1971</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9749</v>
+        <v>0.1565</v>
       </c>
       <c r="L20" t="n">
-        <v>0.065</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2078</v>
+        <v>-1.4091</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5934</v>
+        <v>-0.3131</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3856</v>
+        <v>-1.096</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1684</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1684</v>
+        <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1946</v>
+        <v>0.0464</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5252</v>
+        <v>-0.0867</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3305</v>
+        <v>0.1331</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5521</v>
+        <v>0.2795</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8316</v>
+        <v>0.2795</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6656</v>
+        <v>-0.8307</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9385</v>
+        <v>-0.4193</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2729</v>
+        <v>-0.4114</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.599</v>
+        <v>-2.1177</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2456</v>
+        <v>-2.5683</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3534</v>
+        <v>0.4506</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.711</v>
+        <v>-0.9099</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.1115</v>
+        <v>-0.9749</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5995</v>
+        <v>0.065</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.888</v>
+        <v>-1.2078</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1342</v>
+        <v>-1.5934</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2461</v>
+        <v>0.3856</v>
       </c>
       <c r="P21" t="n">
-        <v>3.3105</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3105</v>
+        <v>1.1684</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5981</v>
+        <v>-0.2651</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4485</v>
+        <v>-0.1726</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1496</v>
+        <v>-0.0925</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2211</v>
+        <v>1.5521</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2211</v>
+        <v>1.8316</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7172</v>
+        <v>-1.9368</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3457</v>
+        <v>-3.1463</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6284999999999999</v>
+        <v>1.2095</v>
       </c>
       <c r="G22" t="n">
         <v>1.623</v>
@@ -2170,13 +2170,13 @@
         <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3939</v>
+        <v>-0.6135</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6045</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.59</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.5590000000000001</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1644</v>
+        <v>-2.5717</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4481</v>
+        <v>-0.5478</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7162</v>
+        <v>-2.0239</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9561</v>
@@ -2248,13 +2248,13 @@
         <v>1.1684</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.292</v>
+        <v>-0.6993</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2012</v>
+        <v>-0.3009</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0908</v>
+        <v>-0.3985</v>
       </c>
       <c r="V23" t="n">
         <v>-0.89</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7827</v>
+        <v>-3.2502</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4777</v>
+        <v>-2.378</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.305</v>
+        <v>-0.8722</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4198</v>
@@ -2326,13 +2326,13 @@
         <v>0.7789</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0571</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.371</v>
+        <v>-0.2713</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6861</v>
+        <v>-0.2533</v>
       </c>
       <c r="V24" t="n">
         <v>-0.89</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.026599999999997</v>
+        <v>6.342700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2801</v>
+        <v>1.280299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2534000000000003</v>
+        <v>5.062499999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.5661</v>
@@ -2392,7 +2392,7 @@
         <v>-6.571899999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4349999999999997</v>
+        <v>0.4349999999999998</v>
       </c>
       <c r="P25" t="n">
         <v>7.789300000000001</v>
@@ -2404,13 +2404,13 @@
         <v>23.3683</v>
       </c>
       <c r="S25" t="n">
-        <v>-12.4409</v>
+        <v>-7.1248</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.9591</v>
+        <v>-3.9592</v>
       </c>
       <c r="U25" t="n">
-        <v>-8.4817</v>
+        <v>-3.1657</v>
       </c>
       <c r="V25" t="n">
         <v>5.112200000000001</v>
